--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO ALEGA CANTABRIA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO ALEGA CANTABRIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>34.8283</v>
+        <v>26.6691</v>
       </c>
       <c r="E2" t="n">
-        <v>32.3125</v>
+        <v>20.5025</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5159</v>
+        <v>6.1671</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.650799999999999</v>
+        <v>-10.3068</v>
       </c>
       <c r="H2" t="n">
-        <v>5.819599999999999</v>
+        <v>-4.9282</v>
       </c>
       <c r="I2" t="n">
-        <v>-10.4703</v>
+        <v>-5.3786</v>
       </c>
       <c r="J2" t="n">
-        <v>22.7554</v>
+        <v>19.2536</v>
       </c>
       <c r="K2" t="n">
-        <v>15.1108</v>
+        <v>8.803000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>7.644100000000001</v>
+        <v>10.451</v>
       </c>
       <c r="M2" t="n">
-        <v>-27.4059</v>
+        <v>-29.5605</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.290900000000001</v>
+        <v>-13.7315</v>
       </c>
       <c r="O2" t="n">
-        <v>-18.1149</v>
+        <v>-15.8294</v>
       </c>
       <c r="P2" t="n">
-        <v>-17.6183</v>
+        <v>6.307499999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-53.289</v>
+        <v>-38.281</v>
       </c>
       <c r="R2" t="n">
-        <v>35.6706</v>
+        <v>44.5886</v>
       </c>
       <c r="S2" t="n">
-        <v>13.878</v>
+        <v>3.261299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>6.552</v>
+        <v>-2.2289</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3262</v>
+        <v>5.4899</v>
       </c>
       <c r="V2" t="n">
-        <v>43.2188</v>
+        <v>27.4075</v>
       </c>
       <c r="W2" t="n">
-        <v>56.2943</v>
+        <v>41.7586</v>
       </c>
       <c r="X2" t="n">
-        <v>-13.0755</v>
+        <v>-14.3511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>24.1467</v>
+        <v>24.1657</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7419</v>
+        <v>23.7614</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4044</v>
+        <v>0.4048000000000002</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.3068</v>
+        <v>-4.650799999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.9282</v>
+        <v>5.819599999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.3786</v>
+        <v>-10.4703</v>
       </c>
       <c r="J3" t="n">
-        <v>19.2536</v>
+        <v>22.7554</v>
       </c>
       <c r="K3" t="n">
-        <v>8.803000000000001</v>
+        <v>15.1108</v>
       </c>
       <c r="L3" t="n">
-        <v>10.451</v>
+        <v>7.644100000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-29.5605</v>
+        <v>-27.4059</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.7315</v>
+        <v>-9.290900000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-15.8294</v>
+        <v>-18.1149</v>
       </c>
       <c r="P3" t="n">
-        <v>6.307499999999999</v>
+        <v>-17.6183</v>
       </c>
       <c r="Q3" t="n">
-        <v>-38.281</v>
+        <v>-53.289</v>
       </c>
       <c r="R3" t="n">
-        <v>44.5886</v>
+        <v>35.6706</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7388999999999992</v>
+        <v>3.216</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.988799999999999</v>
+        <v>-1.9993</v>
       </c>
       <c r="U3" t="n">
-        <v>6.7275</v>
+        <v>5.2153</v>
       </c>
       <c r="V3" t="n">
-        <v>27.4075</v>
+        <v>43.2188</v>
       </c>
       <c r="W3" t="n">
-        <v>41.7586</v>
+        <v>56.2943</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.3511</v>
+        <v>-13.0755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>J. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8.9467</v>
+        <v>6.3165</v>
       </c>
       <c r="E4" t="n">
-        <v>8.210700000000001</v>
+        <v>20.8345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7358000000000002</v>
+        <v>-14.5181</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.9484</v>
+        <v>19.4108</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.627199999999999</v>
+        <v>1.383600000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-9.321200000000001</v>
+        <v>18.0274</v>
       </c>
       <c r="J4" t="n">
-        <v>15.333</v>
+        <v>31.3809</v>
       </c>
       <c r="K4" t="n">
-        <v>14.7411</v>
+        <v>5.240600000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5913000000000004</v>
+        <v>26.1405</v>
       </c>
       <c r="M4" t="n">
-        <v>-26.2815</v>
+        <v>-11.9702</v>
       </c>
       <c r="N4" t="n">
-        <v>-16.3684</v>
+        <v>-3.8572</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.912700000000001</v>
+        <v>-8.113</v>
       </c>
       <c r="P4" t="n">
-        <v>11.5277</v>
+        <v>-8.9178</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.0954</v>
+        <v>-22.4032</v>
       </c>
       <c r="R4" t="n">
-        <v>27.623</v>
+        <v>13.4853</v>
       </c>
       <c r="S4" t="n">
-        <v>17.1869</v>
+        <v>-3.0158</v>
       </c>
       <c r="T4" t="n">
-        <v>9.825200000000001</v>
+        <v>-1.3748</v>
       </c>
       <c r="U4" t="n">
-        <v>7.3615</v>
+        <v>-1.6413</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.819900000000001</v>
+        <v>-1.160700000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.8521</v>
+        <v>13.2314</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.9678</v>
+        <v>-14.3922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PEREZ PEREZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.983199999999998</v>
+        <v>-1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>19.1438</v>
+        <v>1.882</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.1604</v>
+        <v>-3.4028</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4108</v>
+        <v>0.3321999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>1.383600000000001</v>
+        <v>0.4589000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>18.0274</v>
+        <v>-0.1266</v>
       </c>
       <c r="J5" t="n">
-        <v>31.3809</v>
+        <v>2.4202</v>
       </c>
       <c r="K5" t="n">
-        <v>5.240600000000001</v>
+        <v>1.8066</v>
       </c>
       <c r="L5" t="n">
-        <v>26.1405</v>
+        <v>0.6135</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.9702</v>
+        <v>-2.0881</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.8572</v>
+        <v>-1.3477</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.113</v>
+        <v>-0.7404000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.9178</v>
+        <v>1.9575</v>
       </c>
       <c r="Q5" t="n">
-        <v>-22.4032</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>13.4853</v>
+        <v>1.9575</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.349</v>
+        <v>-1.3555</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.0652</v>
+        <v>-0.5384</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.2837</v>
+        <v>-0.8172</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.160700000000001</v>
+        <v>-2.4552</v>
       </c>
       <c r="W5" t="n">
-        <v>13.2314</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-14.3922</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1829</v>
+        <v>-1.6863</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5899</v>
+        <v>5.6241</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7728</v>
+        <v>-7.3103</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3321999999999998</v>
+        <v>-0.9541000000000004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4589000000000001</v>
+        <v>-4.4638</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1266</v>
+        <v>3.5098</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4202</v>
+        <v>18.838</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8066</v>
+        <v>6.3799</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6135</v>
+        <v>12.458</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0881</v>
+        <v>-19.792</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3477</v>
+        <v>-10.8439</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7404000000000001</v>
+        <v>-8.948399999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9575</v>
+        <v>0.6523000000000002</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-21.533</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9575</v>
+        <v>22.1858</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0174</v>
+        <v>-8.578099999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8304000000000001</v>
+        <v>-7.234</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1871</v>
+        <v>-1.344</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4552</v>
+        <v>7.1934</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>15.5531</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4552</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ADDAE-WUSU</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.9447</v>
+        <v>-1.729500000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7794</v>
+        <v>-1.988</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1653</v>
+        <v>0.2584000000000004</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1256</v>
+        <v>-10.9484</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.618</v>
+        <v>-1.627199999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-9.321200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1094</v>
+        <v>15.333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0672</v>
+        <v>14.7411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9578</v>
+        <v>0.5913000000000004</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0162</v>
+        <v>-26.2815</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5508</v>
+        <v>-16.3684</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4654</v>
+        <v>-9.912700000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0451</v>
+        <v>11.5277</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>-16.0954</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>27.623</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5343</v>
+        <v>6.5104</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2896</v>
+        <v>-0.3737000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8239</v>
+        <v>6.8841</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7602</v>
+        <v>-8.819900000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3904</v>
+        <v>-0.8521</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>-7.9678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. LUTETE IV</t>
+          <t>D. ADDAE-WUSU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.743500000000001</v>
+        <v>-4.8215</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.4726</v>
+        <v>-3.7794</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.270999999999999</v>
+        <v>-1.042</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7992999999999995</v>
+        <v>-2.1256</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9944</v>
+        <v>-1.618</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1954</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>9.3743</v>
+        <v>-0.1094</v>
       </c>
       <c r="K8" t="n">
-        <v>4.0996</v>
+        <v>-1.0672</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2745</v>
+        <v>0.9578</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.1734</v>
+        <v>-2.0162</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.0942</v>
+        <v>-0.5508</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.0792</v>
+        <v>-1.4654</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.8302</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q8" t="n">
-        <v>-18.0528</v>
+        <v>-4.3501</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2227</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>2.952199999999999</v>
+        <v>-0.411</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.9407</v>
+        <v>0.2896</v>
       </c>
       <c r="U8" t="n">
-        <v>4.8927</v>
+        <v>-0.7006</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.066</v>
+        <v>0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>5.147</v>
+        <v>0.3904</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.213</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>C. LUTETE IV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.9775</v>
+        <v>-7.0638</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7894</v>
+        <v>-4.4162</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.7669</v>
+        <v>-2.6475</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.9359</v>
+        <v>-0.7992999999999995</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.9575</v>
+        <v>-1.9944</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.978199999999999</v>
+        <v>1.1954</v>
       </c>
       <c r="J9" t="n">
-        <v>20.3364</v>
+        <v>9.3743</v>
       </c>
       <c r="K9" t="n">
-        <v>14.2348</v>
+        <v>4.0996</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1008</v>
+        <v>5.2745</v>
       </c>
       <c r="M9" t="n">
-        <v>-31.2726</v>
+        <v>-10.1734</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.1925</v>
+        <v>-6.0942</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.0798</v>
+        <v>-4.0792</v>
       </c>
       <c r="P9" t="n">
-        <v>9.5702</v>
+        <v>-7.8302</v>
       </c>
       <c r="Q9" t="n">
-        <v>-26.9704</v>
+        <v>-18.0528</v>
       </c>
       <c r="R9" t="n">
-        <v>36.5406</v>
+        <v>10.2227</v>
       </c>
       <c r="S9" t="n">
-        <v>11.7579</v>
+        <v>2.6319</v>
       </c>
       <c r="T9" t="n">
-        <v>6.0853</v>
+        <v>-0.8841000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>5.6722</v>
+        <v>3.516</v>
       </c>
       <c r="V9" t="n">
-        <v>-17.37</v>
+        <v>-1.066</v>
       </c>
       <c r="W9" t="n">
-        <v>12.3379</v>
+        <v>5.147</v>
       </c>
       <c r="X9" t="n">
-        <v>-29.7079</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.3375</v>
+        <v>-15.1459</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7607999999999997</v>
+        <v>-10.6066</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.097999999999999</v>
+        <v>-4.5392</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9541000000000004</v>
+        <v>-5.229200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4638</v>
+        <v>-3.4372</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5098</v>
+        <v>-1.7921</v>
       </c>
       <c r="J10" t="n">
-        <v>18.838</v>
+        <v>-4.0065</v>
       </c>
       <c r="K10" t="n">
-        <v>6.3799</v>
+        <v>-1.7182</v>
       </c>
       <c r="L10" t="n">
-        <v>12.458</v>
+        <v>-2.2889</v>
       </c>
       <c r="M10" t="n">
-        <v>-19.792</v>
+        <v>-1.2229</v>
       </c>
       <c r="N10" t="n">
-        <v>-10.8439</v>
+        <v>-1.7194</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.948399999999999</v>
+        <v>0.4959999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6523000000000002</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q10" t="n">
-        <v>-21.533</v>
+        <v>-5.8726</v>
       </c>
       <c r="R10" t="n">
-        <v>22.1858</v>
+        <v>3.915</v>
       </c>
       <c r="S10" t="n">
-        <v>-15.2291</v>
+        <v>-2.2579</v>
       </c>
       <c r="T10" t="n">
-        <v>-12.0971</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.1318</v>
+        <v>-1.335</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1934</v>
+        <v>-5.7014</v>
       </c>
       <c r="W10" t="n">
-        <v>15.5531</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.359999999999999</v>
+        <v>-5.896599999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.4293</v>
+        <v>-16.5417</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.4277</v>
+        <v>5.964799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0014</v>
+        <v>-22.5067</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.229200000000001</v>
+        <v>26.5519</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4372</v>
+        <v>18.4056</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7921</v>
+        <v>8.146400000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.0065</v>
+        <v>65.35509999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7182</v>
+        <v>39.8885</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2889</v>
+        <v>25.467</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2229</v>
+        <v>-38.8032</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7194</v>
+        <v>-21.4829</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4959999999999999</v>
+        <v>-17.3205</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9576</v>
+        <v>-41.9788</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8726</v>
+        <v>-92.0051</v>
       </c>
       <c r="R11" t="n">
-        <v>3.915</v>
+        <v>50.0264</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.541</v>
+        <v>-10.7831</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2558999999999999</v>
+        <v>-11.1671</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.7971</v>
+        <v>0.3837999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.7014</v>
+        <v>9.668299999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>43.782</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.896599999999999</v>
+        <v>-34.1141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. LOVE</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.3491</v>
+        <v>-17.5158</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.668</v>
+        <v>2.7768</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.681000000000001</v>
+        <v>-20.2924</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.3969</v>
+        <v>-10.9359</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.8846</v>
+        <v>-5.9575</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5123</v>
+        <v>-4.978199999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3677000000000006</v>
+        <v>20.3364</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5529</v>
+        <v>14.2348</v>
       </c>
       <c r="L12" t="n">
-        <v>1.920500000000001</v>
+        <v>6.1008</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.7646</v>
+        <v>-31.2726</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.3315</v>
+        <v>-20.1925</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4329</v>
+        <v>-11.0798</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4802</v>
+        <v>9.5702</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.0052</v>
+        <v>-26.9704</v>
       </c>
       <c r="R12" t="n">
-        <v>6.524999999999999</v>
+        <v>36.5406</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8873</v>
+        <v>1.2198</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.616</v>
+        <v>-2.9272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2714000000000001</v>
+        <v>4.1469</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.5847</v>
+        <v>-17.37</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5856000000000001</v>
+        <v>12.3379</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.170299999999999</v>
+        <v>-29.7079</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. VAN OOSTRUM</t>
+          <t>D. LOVE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-31.0449</v>
+        <v>-18.2623</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.2228</v>
+        <v>-10.7919</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.8218</v>
+        <v>-7.4704</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.8018</v>
+        <v>-6.3969</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0268</v>
+        <v>-4.8846</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.8284</v>
+        <v>-1.5123</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4206</v>
+        <v>0.3677000000000006</v>
       </c>
       <c r="K13" t="n">
-        <v>8.7262</v>
+        <v>-1.5529</v>
       </c>
       <c r="L13" t="n">
-        <v>-10.147</v>
+        <v>1.920500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.3813</v>
+        <v>-6.7646</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.6997</v>
+        <v>-3.3315</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.6814</v>
+        <v>-3.4329</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.4403</v>
+        <v>-3.4802</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.8805</v>
+        <v>-10.0052</v>
       </c>
       <c r="R13" t="n">
-        <v>10.44</v>
+        <v>6.524999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.0718</v>
+        <v>-1.8009</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.1373</v>
+        <v>-1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.935</v>
+        <v>-0.06069999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2691000000000001</v>
+        <v>-6.5847</v>
       </c>
       <c r="W13" t="n">
-        <v>3.2154</v>
+        <v>0.5856000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.9462</v>
+        <v>-7.170299999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>D. VAN OOSTRUM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>-33.47320000000001</v>
+        <v>-27.7058</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.4642</v>
+        <v>-22.4902</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.0088</v>
+        <v>-5.2158</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.407500000000001</v>
+        <v>-12.8018</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.956099999999999</v>
+        <v>1.0268</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5483000000000001</v>
+        <v>-13.8284</v>
       </c>
       <c r="J14" t="n">
-        <v>14.7484</v>
+        <v>-1.4206</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9478</v>
+        <v>8.7262</v>
       </c>
       <c r="L14" t="n">
-        <v>12.8007</v>
+        <v>-10.147</v>
       </c>
       <c r="M14" t="n">
-        <v>-23.1559</v>
+        <v>-11.3813</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.9037</v>
+        <v>-7.6997</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.2522</v>
+        <v>-3.6814</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.2229</v>
+        <v>-10.4403</v>
       </c>
       <c r="Q14" t="n">
-        <v>-40.6738</v>
+        <v>-20.8805</v>
       </c>
       <c r="R14" t="n">
-        <v>30.4506</v>
+        <v>10.44</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1337000000000003</v>
+        <v>-4.732699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.3356</v>
+        <v>-3.4043</v>
       </c>
       <c r="U14" t="n">
-        <v>4.202</v>
+        <v>-1.3287</v>
       </c>
       <c r="V14" t="n">
-        <v>-14.7091</v>
+        <v>0.2691000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7968</v>
+        <v>3.2154</v>
       </c>
       <c r="X14" t="n">
-        <v>-25.5058</v>
+        <v>-2.9462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.8691</v>
+        <v>-29.8461</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.5577</v>
+        <v>-3.8788</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.3111</v>
+        <v>-25.968</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.8386</v>
+        <v>-14.7875</v>
       </c>
       <c r="H15" t="n">
-        <v>-17.644</v>
+        <v>-16.8644</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.1947</v>
+        <v>2.076599999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.5172</v>
+        <v>20.8432</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.6659</v>
+        <v>0.5619999999999994</v>
       </c>
       <c r="L15" t="n">
-        <v>1.148300000000001</v>
+        <v>20.2807</v>
       </c>
       <c r="M15" t="n">
-        <v>-20.3217</v>
+        <v>-35.6305</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.9785</v>
+        <v>-17.4266</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.3434</v>
+        <v>-18.2042</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.1777</v>
+        <v>0.6521999999999997</v>
       </c>
       <c r="Q15" t="n">
-        <v>-21.7506</v>
+        <v>-40.0209</v>
       </c>
       <c r="R15" t="n">
-        <v>14.5727</v>
+        <v>40.6733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2770999999999997</v>
+        <v>-9.341699999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.4572</v>
+        <v>-6.776199999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>3.7341</v>
+        <v>-2.5657</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.1294</v>
+        <v>-6.369</v>
       </c>
       <c r="W15" t="n">
-        <v>8.167199999999999</v>
+        <v>22.0761</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.2967</v>
+        <v>-28.4451</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.7489</v>
+        <v>-30.2791</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.501700000000001</v>
+        <v>-18.0579</v>
       </c>
       <c r="F16" t="n">
-        <v>-30.2476</v>
+        <v>-12.2205</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.7875</v>
+        <v>-8.407500000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-16.8644</v>
+        <v>-8.956099999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.076599999999999</v>
+        <v>0.5483000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>20.8432</v>
+        <v>14.7484</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5619999999999994</v>
+        <v>1.9478</v>
       </c>
       <c r="L16" t="n">
-        <v>20.2807</v>
+        <v>12.8007</v>
       </c>
       <c r="M16" t="n">
-        <v>-35.6305</v>
+        <v>-23.1559</v>
       </c>
       <c r="N16" t="n">
-        <v>-17.4266</v>
+        <v>-10.9037</v>
       </c>
       <c r="O16" t="n">
-        <v>-18.2042</v>
+        <v>-12.2522</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6521999999999997</v>
+        <v>-10.2229</v>
       </c>
       <c r="Q16" t="n">
-        <v>-40.0209</v>
+        <v>-40.6738</v>
       </c>
       <c r="R16" t="n">
-        <v>40.6733</v>
+        <v>30.4506</v>
       </c>
       <c r="S16" t="n">
-        <v>-17.245</v>
+        <v>3.0606</v>
       </c>
       <c r="T16" t="n">
-        <v>-10.3991</v>
+        <v>-2.9294</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.8457</v>
+        <v>5.99</v>
       </c>
       <c r="V16" t="n">
-        <v>-6.369</v>
+        <v>-14.7091</v>
       </c>
       <c r="W16" t="n">
-        <v>22.0761</v>
+        <v>10.7968</v>
       </c>
       <c r="X16" t="n">
-        <v>-28.4451</v>
+        <v>-25.5058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>-40.2893</v>
+        <v>-36.6256</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.437100000000001</v>
+        <v>-21.0661</v>
       </c>
       <c r="F17" t="n">
-        <v>-31.8521</v>
+        <v>-15.5593</v>
       </c>
       <c r="G17" t="n">
-        <v>26.5519</v>
+        <v>-23.8386</v>
       </c>
       <c r="H17" t="n">
-        <v>18.4056</v>
+        <v>-17.644</v>
       </c>
       <c r="I17" t="n">
-        <v>8.146400000000002</v>
+        <v>-6.1947</v>
       </c>
       <c r="J17" t="n">
-        <v>65.35509999999999</v>
+        <v>-3.5172</v>
       </c>
       <c r="K17" t="n">
-        <v>39.8885</v>
+        <v>-4.6659</v>
       </c>
       <c r="L17" t="n">
-        <v>25.467</v>
+        <v>1.148300000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-38.8032</v>
+        <v>-20.3217</v>
       </c>
       <c r="N17" t="n">
-        <v>-21.4829</v>
+        <v>-12.9785</v>
       </c>
       <c r="O17" t="n">
-        <v>-17.3205</v>
+        <v>-7.3434</v>
       </c>
       <c r="P17" t="n">
-        <v>-41.9788</v>
+        <v>-7.1777</v>
       </c>
       <c r="Q17" t="n">
-        <v>-92.0051</v>
+        <v>-21.7506</v>
       </c>
       <c r="R17" t="n">
-        <v>50.0264</v>
+        <v>14.5727</v>
       </c>
       <c r="S17" t="n">
-        <v>-34.5304</v>
+        <v>-1.4794</v>
       </c>
       <c r="T17" t="n">
-        <v>-25.5692</v>
+        <v>-3.9655</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.9612</v>
+        <v>2.4859</v>
       </c>
       <c r="V17" t="n">
-        <v>9.668299999999999</v>
+        <v>-4.1294</v>
       </c>
       <c r="W17" t="n">
-        <v>43.782</v>
+        <v>8.167199999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-34.1141</v>
+        <v>-12.2967</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>-64.7675</v>
+        <v>-52.4341</v>
       </c>
       <c r="E18" t="n">
-        <v>-41.8234</v>
+        <v>-35.0891</v>
       </c>
       <c r="F18" t="n">
-        <v>-22.9443</v>
+        <v>-17.3447</v>
       </c>
       <c r="G18" t="n">
         <v>-0.08100000000000152</v>
@@ -1858,13 +1858,13 @@
         <v>36.9755</v>
       </c>
       <c r="S18" t="n">
-        <v>-22.5027</v>
+        <v>-10.1682</v>
       </c>
       <c r="T18" t="n">
-        <v>-14.8613</v>
+        <v>-8.126300000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-7.6415</v>
+        <v>-2.0418</v>
       </c>
       <c r="V18" t="n">
         <v>-9.993300000000001</v>
@@ -1891,16 +1891,16 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>-233.2525</v>
+        <v>-204.0272</v>
       </c>
       <c r="E19" t="n">
-        <v>-62.80559999999999</v>
+        <v>-50.81809999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-170.4464</v>
+        <v>-153.2074</v>
       </c>
       <c r="G19" t="n">
-        <v>-65.96850000000001</v>
+        <v>-65.96850000000002</v>
       </c>
       <c r="H19" t="n">
         <v>-47.8403</v>
@@ -1936,16 +1936,16 @@
         <v>387.1576</v>
       </c>
       <c r="S19" t="n">
-        <v>-63.25070000000001</v>
+        <v>-34.0243</v>
       </c>
       <c r="T19" t="n">
-        <v>-68.2899</v>
+        <v>-56.3025</v>
       </c>
       <c r="U19" t="n">
-        <v>5.037800000000003</v>
+        <v>22.2769</v>
       </c>
       <c r="V19" t="n">
-        <v>10.15860000000001</v>
+        <v>10.1586</v>
       </c>
       <c r="W19" t="n">
         <v>251.7346</v>
